--- a/artfynd/A 32736-2023 artfynd.xlsx
+++ b/artfynd/A 32736-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32736-2023 artfynd.xlsx
+++ b/artfynd/A 32736-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103003758</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553059.168373352</v>
+        <v>553059</v>
       </c>
       <c r="R2" t="n">
-        <v>7012653.403902887</v>
+        <v>7012654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-06-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103003745</v>
+        <v>103003775</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553035.5391719553</v>
+        <v>553066</v>
       </c>
       <c r="R3" t="n">
-        <v>7012690.427604211</v>
+        <v>7012742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +852,9 @@
           <t>2022-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,6 +879,216 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>103003745</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>553035</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7012690</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103003784</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>553078</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7012774</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 32736-2023 artfynd.xlsx
+++ b/artfynd/A 32736-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103003758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103003775</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103003745</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,8 +1113,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103003784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>